--- a/Excel/00_Planilla.xlsx
+++ b/Excel/00_Planilla.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mac\Home\Documents\Relatorias\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8A4FA6-45FB-4217-8A67-3F0F8F83FCAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085FE5E5-03F7-45FB-A34A-CAB3D1E2809E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="14700" activeTab="3" xr2:uid="{D425D257-4975-4662-9275-A17F5F694604}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="14700" xr2:uid="{D425D257-4975-4662-9275-A17F5F694604}"/>
   </bookViews>
   <sheets>
     <sheet name="P1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,14 @@
     <sheet name="P8" sheetId="8" r:id="rId8"/>
     <sheet name="Ejercicio" sheetId="9" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'P7'!$A$1:$F$21</definedName>
+    <definedName name="Z_8604812A_736C_47AE_A298_3A6F79AFD00F_.wvu.FilterData" localSheetId="6" hidden="1">'P7'!$A$1:$F$21</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <customWorkbookViews>
+    <customWorkbookView name="1" guid="{8604812A-736C-47AE-A298-3A6F79AFD00F}" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1696" windowHeight="980" activeSheetId="8"/>
+  </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="55">
   <si>
     <t xml:space="preserve">Fecha </t>
   </si>
@@ -203,13 +210,22 @@
   </si>
   <si>
     <t>Temperatura (C º)</t>
+  </si>
+  <si>
+    <t>Lenctura final</t>
+  </si>
+  <si>
+    <t>Caldera 4</t>
+  </si>
+  <si>
+    <t>Caldera 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,6 +248,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
@@ -244,8 +267,16 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -261,12 +292,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -298,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -316,17 +341,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -547,7 +586,7 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>436245</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>145039</xdr:rowOff>
+      <xdr:rowOff>141864</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -592,7 +631,7 @@
       <xdr:col>30</xdr:col>
       <xdr:colOff>611369</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>159701</xdr:rowOff>
+      <xdr:rowOff>162876</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -635,9 +674,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>655637</xdr:colOff>
+      <xdr:colOff>658812</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>101657</xdr:rowOff>
+      <xdr:rowOff>104832</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -770,14 +809,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>780843</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>666543</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
@@ -802,8 +841,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4733718" y="0"/>
-          <a:ext cx="6572457" cy="2466975"/>
+          <a:off x="6000543" y="0"/>
+          <a:ext cx="6331157" cy="2466975"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -819,14 +858,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>771525</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>454025</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>577850</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>97129</xdr:rowOff>
     </xdr:to>
@@ -851,8 +890,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4724400" y="0"/>
-          <a:ext cx="5676900" cy="2268829"/>
+          <a:off x="6550025" y="0"/>
+          <a:ext cx="5457825" cy="2268829"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -869,15 +908,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>647700</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>7622</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>658</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>174011</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -901,8 +940,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5534025" y="7622"/>
-          <a:ext cx="5724525" cy="2164736"/>
+          <a:off x="6238875" y="0"/>
+          <a:ext cx="5524500" cy="2164736"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -918,16 +957,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>781050</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>37744</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>133348</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>71285</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -942,16 +981,17 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
+      <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect l="870" b="7280"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6315075" y="0"/>
-          <a:ext cx="9448800" cy="2390419"/>
+          <a:off x="8498416" y="0"/>
+          <a:ext cx="8420099" cy="2050368"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1333,8 +1373,15 @@
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
+  <customSheetViews>
+    <customSheetView guid="{8604812A-736C-47AE-A298-3A6F79AFD00F}" scale="120">
+      <selection activeCell="H17" sqref="H17"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+  </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1529,90 +1576,103 @@
       </c>
     </row>
   </sheetData>
+  <customSheetViews>
+    <customSheetView guid="{8604812A-736C-47AE-A298-3A6F79AFD00F}">
+      <selection activeCell="B73" sqref="B73"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+  </customSheetViews>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E427FEF-26E0-439F-914B-EFBCE7FFCB8A}">
   <sheetPr codeName="Hoja3"/>
-  <dimension ref="B2:U4"/>
+  <dimension ref="P2:U4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="6.90625" style="7" customWidth="1"/>
-    <col min="16" max="16" width="8.08984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.08984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.08984375" style="10" customWidth="1"/>
-    <col min="19" max="19" width="7.90625" style="10" customWidth="1"/>
-    <col min="20" max="20" width="10.81640625" style="10" customWidth="1"/>
-    <col min="21" max="21" width="10.90625" style="10"/>
+    <col min="16" max="16" width="8.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.08984375" style="9" customWidth="1"/>
+    <col min="19" max="19" width="7.90625" style="9" customWidth="1"/>
+    <col min="20" max="20" width="10.81640625" style="9" customWidth="1"/>
+    <col min="21" max="21" width="10.90625" style="9"/>
   </cols>
   <sheetData>
     <row r="2" spans="16:21" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="Q2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="R2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="S2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="8" t="s">
+      <c r="T2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="U2" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="16:21" x14ac:dyDescent="0.35">
-      <c r="P3" s="11">
+      <c r="P3" s="10">
         <v>46276</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="R3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="S3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="T3" s="9">
+      <c r="T3" s="8">
         <v>82</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="U3" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="16:21" x14ac:dyDescent="0.35">
-      <c r="P4" s="11">
+      <c r="P4" s="10">
         <v>46276</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="R4" s="9" t="s">
+      <c r="R4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="S4" s="9" t="s">
+      <c r="S4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="9">
+      <c r="T4" s="8">
         <v>78</v>
       </c>
-      <c r="U4" s="9" t="s">
+      <c r="U4" s="8" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <customSheetViews>
+    <customSheetView guid="{8604812A-736C-47AE-A298-3A6F79AFD00F}" scale="120" topLeftCell="M1">
+      <selection activeCell="S22" sqref="S22"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+  </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1732,52 +1792,836 @@
       <c r="T7" s="1"/>
     </row>
   </sheetData>
+  <customSheetViews>
+    <customSheetView guid="{8604812A-736C-47AE-A298-3A6F79AFD00F}" topLeftCell="R1">
+      <selection activeCell="AA26" sqref="AA26"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+  </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D86651-0814-4D21-9916-E30701F7F1E6}">
   <sheetPr codeName="Hoja5"/>
-  <dimension ref="A1"/>
+  <dimension ref="B1:E4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="5" width="13.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>120</v>
+      </c>
+      <c r="D2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>98</v>
+      </c>
+      <c r="D3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4">
+        <v>150</v>
+      </c>
+      <c r="D4">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
+  <customSheetViews>
+    <customSheetView guid="{8604812A-736C-47AE-A298-3A6F79AFD00F}">
+      <selection activeCell="B1" sqref="B1:E4"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+  </customSheetViews>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5868F6E9-1710-4E1D-8554-30D1B795AF6B}">
   <sheetPr codeName="Hoja6"/>
-  <dimension ref="A1"/>
+  <dimension ref="B1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <customSheetViews>
+    <customSheetView guid="{8604812A-736C-47AE-A298-3A6F79AFD00F}">
+      <selection activeCell="F6" sqref="F6"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+  </customSheetViews>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5717829A-3788-432D-B9D3-0C993DB4373F}">
   <sheetPr codeName="Hoja7"/>
-  <dimension ref="A1"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="5" width="11.453125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.90625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="12">
+        <v>46266</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="11">
+        <v>82</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="12">
+        <v>46275</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="11">
+        <v>80</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="12">
+        <v>46274</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="11">
+        <v>78</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="12">
+        <v>46274</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="11">
+        <v>85</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="12">
+        <v>46273</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="11">
+        <v>87</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="12">
+        <v>46267</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="11">
+        <v>81</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="12">
+        <v>46269</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="11">
+        <v>83</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="12">
+        <v>46272</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="11">
+        <v>79</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="12">
+        <v>46271</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="11">
+        <v>77</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="12">
+        <v>46271</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="11">
+        <v>84</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="12">
+        <v>46270</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="11">
+        <v>86</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="12">
+        <v>46270</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="11">
+        <v>82</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="12">
+        <v>46272</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="11">
+        <v>81</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="12">
+        <v>46269</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="11">
+        <v>80</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="12">
+        <v>46268</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="11">
+        <v>78</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="12">
+        <v>46268</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="11">
+        <v>84</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="12">
+        <v>46267</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="11">
+        <v>85</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="12">
+        <v>46273</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="11">
+        <v>83</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="12">
+        <v>46275</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="11">
+        <v>82</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="12">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="11">
+        <v>79</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F21">
+    <sortCondition descending="1" ref="A2:A21"/>
+    <sortCondition ref="B2:B21"/>
+  </sortState>
+  <customSheetViews>
+    <customSheetView guid="{8604812A-736C-47AE-A298-3A6F79AFD00F}">
+      <selection activeCell="H14" sqref="H14"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+  </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE9B4355-CC4F-4B65-9B96-DC462D50CC43}">
-  <sheetPr codeName="Hoja8"/>
-  <dimension ref="A1"/>
+  <sheetPr codeName="Hoja8">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <cols>
+    <col min="1" max="1" width="11.26953125" customWidth="1"/>
+    <col min="2" max="2" width="8.54296875" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.54296875" customWidth="1"/>
+    <col min="9" max="9" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="14">
+        <v>46266</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="15">
+        <v>120</v>
+      </c>
+      <c r="E2" s="15">
+        <v>135</v>
+      </c>
+      <c r="F2" s="15">
+        <v>15</v>
+      </c>
+      <c r="G2" s="15">
+        <v>82</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="14">
+        <v>46266</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="15">
+        <v>98</v>
+      </c>
+      <c r="E3" s="15">
+        <v>110</v>
+      </c>
+      <c r="F3" s="15">
+        <v>12</v>
+      </c>
+      <c r="G3" s="15">
+        <v>79</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="14">
+        <v>46267</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="15">
+        <v>150</v>
+      </c>
+      <c r="E4" s="15">
+        <v>162</v>
+      </c>
+      <c r="F4" s="15">
+        <v>12</v>
+      </c>
+      <c r="G4" s="15">
+        <v>85</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="14">
+        <v>46267</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="15">
+        <v>130</v>
+      </c>
+      <c r="E5" s="15">
+        <v>142</v>
+      </c>
+      <c r="F5" s="15">
+        <v>12</v>
+      </c>
+      <c r="G5" s="15">
+        <v>81</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="14">
+        <v>46268</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="15">
+        <v>105</v>
+      </c>
+      <c r="E6" s="15">
+        <v>121</v>
+      </c>
+      <c r="F6" s="15">
+        <v>16</v>
+      </c>
+      <c r="G6" s="15">
+        <v>78</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <customSheetViews>
+    <customSheetView guid="{8604812A-736C-47AE-A298-3A6F79AFD00F}" showPageBreaks="1">
+      <selection activeCell="I23" sqref="I22:I23"/>
+      <colBreaks count="1" manualBreakCount="1">
+        <brk id="10" max="1048575" man="1"/>
+      </colBreaks>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="9" scale="83" orientation="portrait" r:id="rId1"/>
+    </customSheetView>
+  </customSheetViews>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="48" orientation="landscape" r:id="rId2"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="10" max="1048575" man="1"/>
+  </colBreaks>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1980,7 +2824,14 @@
       </c>
     </row>
   </sheetData>
+  <customSheetViews>
+    <customSheetView guid="{8604812A-736C-47AE-A298-3A6F79AFD00F}">
+      <selection activeCell="K8" sqref="K8"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+  </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/00_Planilla.xlsx
+++ b/Excel/00_Planilla.xlsx
@@ -8,23 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mac\Home\Documents\Relatorias\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085FE5E5-03F7-45FB-A34A-CAB3D1E2809E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A3F912-32D2-4D5B-8223-EF7C0BC58BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="14700" xr2:uid="{D425D257-4975-4662-9275-A17F5F694604}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="14700" activeTab="9" xr2:uid="{D425D257-4975-4662-9275-A17F5F694604}"/>
   </bookViews>
   <sheets>
     <sheet name="P1" sheetId="1" r:id="rId1"/>
     <sheet name="P2" sheetId="2" r:id="rId2"/>
-    <sheet name="P3" sheetId="3" r:id="rId3"/>
+    <sheet name="Registro diario" sheetId="3" r:id="rId3"/>
     <sheet name="P4" sheetId="4" r:id="rId4"/>
     <sheet name="P5" sheetId="5" r:id="rId5"/>
     <sheet name="P6" sheetId="6" r:id="rId6"/>
     <sheet name="P7" sheetId="7" r:id="rId7"/>
     <sheet name="P8" sheetId="8" r:id="rId8"/>
     <sheet name="Ejercicio" sheetId="9" r:id="rId9"/>
+    <sheet name="Registro Semanal" sheetId="14" r:id="rId10"/>
+    <sheet name="Ejercicio (2)" sheetId="13" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'P2'!$B$72:$F$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'P7'!$A$1:$F$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'P8'!$A$1:$J$6</definedName>
     <definedName name="Z_8604812A_736C_47AE_A298_3A6F79AFD00F_.wvu.FilterData" localSheetId="6" hidden="1">'P7'!$A$1:$F$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -54,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="70">
   <si>
     <t xml:space="preserve">Fecha </t>
   </si>
@@ -101,9 +105,6 @@
     <t>Caldera 2</t>
   </si>
   <si>
-    <t>Revisar</t>
-  </si>
-  <si>
     <t>fecha</t>
   </si>
   <si>
@@ -206,26 +207,74 @@
     <t>ISG</t>
   </si>
   <si>
-    <t>KH</t>
-  </si>
-  <si>
     <t>Temperatura (C º)</t>
   </si>
   <si>
-    <t>Lenctura final</t>
-  </si>
-  <si>
     <t>Caldera 4</t>
   </si>
   <si>
     <t>Caldera 5</t>
+  </si>
+  <si>
+    <t>c4</t>
+  </si>
+  <si>
+    <t>yy</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>Cantidad</t>
+  </si>
+  <si>
+    <t>Valor unitario</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Total de registros</t>
+  </si>
+  <si>
+    <t>Temperatura promedio</t>
+  </si>
+  <si>
+    <t>Temperatura maxima</t>
+  </si>
+  <si>
+    <t>Temperatura minima</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,6 +304,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
@@ -275,8 +331,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -292,6 +363,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -320,10 +427,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -341,16 +449,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -359,18 +467,52 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -435,6 +577,194 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>436245</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>68350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15D588DC-5B09-4C31-94F9-4AB3AECE8570}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect l="204" t="5516" r="6303"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5203824" y="0"/>
+          <a:ext cx="4233546" cy="2466452"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>7937</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>86042</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>611369</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>67138</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEEFA13B-936B-4409-8A9C-56C08106022E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect l="871" t="6947" b="12018"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16003587" y="82867"/>
+          <a:ext cx="6696257" cy="1490198"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>750887</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>177801</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>655637</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>101657</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01637618-E485-4246-94C5-DA49ABFE9B5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15984537" y="1581151"/>
+          <a:ext cx="6000750" cy="2276531"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>19585</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D51EC376-404C-450A-875C-14A53B0E0A8C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9036050" y="0"/>
+          <a:ext cx="11042650" cy="3696235"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -446,7 +776,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>354230</xdr:colOff>
+      <xdr:colOff>351055</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -534,9 +864,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>368301</xdr:colOff>
+      <xdr:colOff>371476</xdr:colOff>
       <xdr:row>78</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -585,8 +915,8 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>436245</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>141864</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>164577</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -630,8 +960,8 @@
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>611369</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>162876</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>172890</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -669,14 +999,14 @@
     <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>750887</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>177801</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>658812</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>104832</xdr:rowOff>
+      <xdr:colOff>655637</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>101657</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -724,8 +1054,8 @@
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>657138</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>112395</xdr:rowOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -769,7 +1099,7 @@
       <xdr:col>32</xdr:col>
       <xdr:colOff>294980</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>17462</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -816,7 +1146,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
+      <xdr:colOff>139700</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
@@ -865,7 +1195,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>577850</xdr:colOff>
+      <xdr:colOff>581025</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>97129</xdr:rowOff>
     </xdr:to>
@@ -907,16 +1237,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>255587</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>26988</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>174011</xdr:rowOff>
+      <xdr:colOff>449262</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>12087</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -940,8 +1270,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6238875" y="0"/>
-          <a:ext cx="5524500" cy="2164736"/>
+          <a:off x="6883400" y="26988"/>
+          <a:ext cx="5524500" cy="2179024"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -965,8 +1295,8 @@
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>133348</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>71285</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>63958</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1369,10 +1699,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D85B78-361D-4872-9F03-FDFBDE13B5A9}">
-  <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1"/>
+  <sheetPr codeName="Hoja1">
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="C4:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="4" max="4" width="4.6328125" style="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C4" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="E5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5" s="17" customFormat="1" x14ac:dyDescent="0.35"/>
+  </sheetData>
   <customSheetViews>
     <customSheetView guid="{8604812A-736C-47AE-A298-3A6F79AFD00F}" scale="120">
       <selection activeCell="H17" sqref="H17"/>
@@ -1385,23 +1732,346 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB7291D4-3D80-4027-B0E7-BE86B33D0B37}">
+  <sheetPr codeName="Hoja9"/>
+  <dimension ref="B2:U15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="8.90625" customWidth="1"/>
+    <col min="16" max="16" width="7.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.36328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.26953125" style="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="P2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="U2" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="2:21" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P3" s="22">
+        <v>46276</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" s="21">
+        <v>82</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="P4" s="23">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="P5" s="23"/>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="P6" s="23"/>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="P7" s="23"/>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="P8" s="23"/>
+    </row>
+    <row r="9" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="P9" s="23"/>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="P10" s="23"/>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="P11" s="23"/>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="P12" s="23"/>
+    </row>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="P13" s="23"/>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="P14" s="23"/>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="P15" s="23"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E6A503-1E96-4F04-8FD8-7356BBBF9F73}">
+  <sheetPr codeName="Hoja11"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4">
+        <v>46266</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="6">
+        <v>120</v>
+      </c>
+      <c r="E2" s="6">
+        <v>135</v>
+      </c>
+      <c r="F2" s="6">
+        <v>15</v>
+      </c>
+      <c r="G2" s="6">
+        <v>82</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>46266</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="6">
+        <v>98</v>
+      </c>
+      <c r="E3" s="6">
+        <v>110</v>
+      </c>
+      <c r="F3" s="6">
+        <v>12</v>
+      </c>
+      <c r="G3" s="6">
+        <v>79</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>46267</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="6">
+        <v>150</v>
+      </c>
+      <c r="E4" s="6">
+        <v>162</v>
+      </c>
+      <c r="F4" s="6">
+        <v>12</v>
+      </c>
+      <c r="G4" s="6">
+        <v>85</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>46267</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="6">
+        <v>130</v>
+      </c>
+      <c r="E5" s="6">
+        <v>142</v>
+      </c>
+      <c r="F5" s="6">
+        <v>12</v>
+      </c>
+      <c r="G5" s="6">
+        <v>81</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>46268</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="6">
+        <v>105</v>
+      </c>
+      <c r="E6" s="6">
+        <v>121</v>
+      </c>
+      <c r="F6" s="6">
+        <v>16</v>
+      </c>
+      <c r="G6" s="6">
+        <v>78</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6B07D38-0D61-43BF-9933-D08267668A2F}">
-  <sheetPr codeName="Hoja2"/>
-  <dimension ref="B2:F72"/>
+  <sheetPr codeName="Hoja2">
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="B2:F79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="2" max="2" width="11.26953125" customWidth="1"/>
+    <col min="3" max="3" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7265625" customWidth="1"/>
     <col min="5" max="5" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="D4" t="s">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
@@ -1409,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F40" s="1">
         <v>46266</v>
@@ -1420,7 +2090,7 @@
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F41" s="1">
         <v>46267</v>
@@ -1431,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F42" s="1">
         <v>46268</v>
@@ -1442,7 +2112,7 @@
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F43" s="1">
         <v>46269</v>
@@ -1453,7 +2123,7 @@
         <v>5</v>
       </c>
       <c r="D44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F44" s="1">
         <v>46270</v>
@@ -1464,7 +2134,7 @@
         <v>6</v>
       </c>
       <c r="D45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F45" s="1">
         <v>46271</v>
@@ -1475,7 +2145,7 @@
         <v>7</v>
       </c>
       <c r="D46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F46" s="1">
         <v>46272</v>
@@ -1486,7 +2156,7 @@
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F47" s="1">
         <v>46273</v>
@@ -1497,7 +2167,7 @@
         <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F48" s="1">
         <v>46274</v>
@@ -1508,7 +2178,7 @@
         <v>10</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F49" s="1">
         <v>46275</v>
@@ -1519,7 +2189,7 @@
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F50" s="1">
         <v>46276</v>
@@ -1530,7 +2200,7 @@
         <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F51" s="1">
         <v>46277</v>
@@ -1541,7 +2211,7 @@
         <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F52" s="1">
         <v>46278</v>
@@ -1552,30 +2222,160 @@
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F53" s="1">
         <v>46279</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B72" t="s">
+    <row r="72" spans="2:6" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B72" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F72" s="20" t="s">
         <v>4</v>
       </c>
     </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B73" s="19">
+        <v>46280</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E73" s="18">
+        <v>80</v>
+      </c>
+      <c r="F73" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B74" s="19">
+        <f>B73+7</f>
+        <v>46287</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E74" s="18">
+        <v>70</v>
+      </c>
+      <c r="F74" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B75" s="19">
+        <f t="shared" ref="B75:B79" si="0">B74+7</f>
+        <v>46294</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E75" s="18">
+        <v>90</v>
+      </c>
+      <c r="F75" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B76" s="19">
+        <f t="shared" si="0"/>
+        <v>46301</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E76" s="18">
+        <f>E75+10</f>
+        <v>100</v>
+      </c>
+      <c r="F76" s="18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B77" s="19">
+        <f t="shared" si="0"/>
+        <v>46308</v>
+      </c>
+      <c r="C77" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E77" s="18">
+        <f t="shared" ref="E77:E78" si="1">E76+10</f>
+        <v>110</v>
+      </c>
+      <c r="F77" s="18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B78" s="19">
+        <f t="shared" si="0"/>
+        <v>46315</v>
+      </c>
+      <c r="C78" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E78" s="18">
+        <f>E77+E73</f>
+        <v>190</v>
+      </c>
+      <c r="F78" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B79" s="19">
+        <f t="shared" si="0"/>
+        <v>46322</v>
+      </c>
+      <c r="C79" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E79" s="18">
+        <f>E78+E74</f>
+        <v>260</v>
+      </c>
+      <c r="F79" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="B72:F79" xr:uid="{B6B07D38-0D61-43BF-9933-D08267668A2F}"/>
   <customSheetViews>
     <customSheetView guid="{8604812A-736C-47AE-A298-3A6F79AFD00F}">
       <selection activeCell="B73" sqref="B73"/>
@@ -1591,50 +2391,56 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E427FEF-26E0-439F-914B-EFBCE7FFCB8A}">
-  <sheetPr codeName="Hoja3"/>
-  <dimension ref="P2:U4"/>
+  <sheetPr codeName="Hoja3">
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="B2:U5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="2" max="2" width="8.90625" customWidth="1"/>
     <col min="16" max="16" width="8.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.08984375" style="9" customWidth="1"/>
-    <col min="19" max="19" width="7.90625" style="9" customWidth="1"/>
+    <col min="17" max="17" width="7.08984375" style="9" customWidth="1"/>
+    <col min="18" max="18" width="7.90625" style="9" customWidth="1"/>
+    <col min="19" max="19" width="11.7265625" style="9" customWidth="1"/>
     <col min="20" max="20" width="10.81640625" style="9" customWidth="1"/>
     <col min="21" max="21" width="10.90625" style="9"/>
   </cols>
   <sheetData>
-    <row r="2" spans="16:21" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:21" ht="21" x14ac:dyDescent="0.35">
       <c r="P2" s="7" t="s">
         <v>5</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="R2" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S2" s="7" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="T2" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U2" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="16:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:21" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
       <c r="P3" s="10">
         <v>46276</v>
       </c>
-      <c r="Q3" s="10" t="s">
-        <v>49</v>
+      <c r="Q3" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="T3" s="8">
         <v>82</v>
@@ -1643,24 +2449,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="16:21" x14ac:dyDescent="0.35">
-      <c r="P4" s="10">
-        <v>46276</v>
-      </c>
-      <c r="Q4" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="T4" s="8">
-        <v>78</v>
-      </c>
-      <c r="U4" s="8" t="s">
-        <v>15</v>
+    <row r="4" spans="2:21" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1678,114 +2474,119 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E38B4D3-C306-43D2-826A-31534B989FF2}">
-  <sheetPr codeName="Hoja4"/>
+  <sheetPr codeName="Hoja4">
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="T1:X7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="23" max="23" width="17.1796875" customWidth="1"/>
-    <col min="24" max="24" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.453125" style="9" customWidth="1"/>
+    <col min="22" max="22" width="10.26953125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="20:24" x14ac:dyDescent="0.35">
-      <c r="T1" t="s">
+    <row r="1" spans="20:24" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T1" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="X1" t="s">
+    </row>
+    <row r="2" spans="20:24" x14ac:dyDescent="0.35">
+      <c r="T2" s="28">
+        <v>46276</v>
+      </c>
+      <c r="U2" s="29" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="20:24" x14ac:dyDescent="0.35">
-      <c r="T2" s="1">
+      <c r="V2" s="30">
+        <v>82</v>
+      </c>
+      <c r="W2" s="31">
+        <v>0.95</v>
+      </c>
+      <c r="X2" s="29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="20:24" x14ac:dyDescent="0.35">
+      <c r="T3" s="28">
         <v>46276</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U3" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="V3" s="30">
+        <v>78</v>
+      </c>
+      <c r="W3" s="31">
+        <v>0.88</v>
+      </c>
+      <c r="X3" s="29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="20:24" x14ac:dyDescent="0.35">
+      <c r="T4" s="28">
+        <v>46277</v>
+      </c>
+      <c r="U4" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="V4" s="30">
+        <v>81</v>
+      </c>
+      <c r="W4" s="31">
+        <v>0.91</v>
+      </c>
+      <c r="X4" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="V2">
-        <v>82</v>
-      </c>
-      <c r="W2">
-        <v>0.95</v>
-      </c>
-      <c r="X2" t="s">
+    </row>
+    <row r="5" spans="20:24" x14ac:dyDescent="0.35">
+      <c r="T5" s="28">
+        <v>46277</v>
+      </c>
+      <c r="U5" s="29" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="20:24" x14ac:dyDescent="0.35">
-      <c r="T3" s="1">
-        <v>46276</v>
-      </c>
-      <c r="U3" t="s">
-        <v>23</v>
-      </c>
-      <c r="V3">
-        <v>78</v>
-      </c>
-      <c r="W3">
-        <v>0.88</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="V5" s="30">
+        <v>79</v>
+      </c>
+      <c r="W5" s="31">
+        <v>0.86</v>
+      </c>
+      <c r="X5" s="29" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="20:24" x14ac:dyDescent="0.35">
-      <c r="T4" s="1">
-        <v>46277</v>
-      </c>
-      <c r="U4" t="s">
+    <row r="6" spans="20:24" x14ac:dyDescent="0.35">
+      <c r="T6" s="28">
+        <v>46278</v>
+      </c>
+      <c r="U6" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="V6" s="30">
+        <v>83</v>
+      </c>
+      <c r="W6" s="31">
+        <v>0.97</v>
+      </c>
+      <c r="X6" s="29" t="s">
         <v>21</v>
-      </c>
-      <c r="V4">
-        <v>81</v>
-      </c>
-      <c r="W4">
-        <v>0.91</v>
-      </c>
-      <c r="X4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="20:24" x14ac:dyDescent="0.35">
-      <c r="T5" s="1">
-        <v>46277</v>
-      </c>
-      <c r="U5" t="s">
-        <v>23</v>
-      </c>
-      <c r="V5">
-        <v>79</v>
-      </c>
-      <c r="W5">
-        <v>0.86</v>
-      </c>
-      <c r="X5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="20:24" x14ac:dyDescent="0.35">
-      <c r="T6" s="1">
-        <v>46278</v>
-      </c>
-      <c r="U6" t="s">
-        <v>21</v>
-      </c>
-      <c r="V6">
-        <v>83</v>
-      </c>
-      <c r="W6">
-        <v>0.97</v>
-      </c>
-      <c r="X6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7" spans="20:24" x14ac:dyDescent="0.35">
@@ -1806,8 +2607,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D86651-0814-4D21-9916-E30701F7F1E6}">
-  <sheetPr codeName="Hoja5"/>
-  <dimension ref="B1:E4"/>
+  <sheetPr codeName="Hoja5">
+    <tabColor theme="8"/>
+  </sheetPr>
+  <dimension ref="B1:E27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="5" width="13.54296875" customWidth="1"/>
@@ -1818,13 +2621,13 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" t="s">
-        <v>52</v>
-      </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.35">
@@ -1837,6 +2640,10 @@
       <c r="D2">
         <v>135</v>
       </c>
+      <c r="E2">
+        <f>D2-C2</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
@@ -1848,16 +2655,47 @@
       <c r="D3">
         <v>110</v>
       </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E4" si="0">D3-C3</f>
+        <v>12</v>
+      </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D4">
         <v>162</v>
+      </c>
+      <c r="E4">
+        <f>D4-C4</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27">
+        <v>2500</v>
+      </c>
+      <c r="E27">
+        <f>C27*D27</f>
+        <v>12500</v>
       </c>
     </row>
   </sheetData>
@@ -1877,13 +2715,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5868F6E9-1710-4E1D-8554-30D1B795AF6B}">
   <sheetPr codeName="Hoja6"/>
-  <dimension ref="B1:C6"/>
+  <dimension ref="B1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="5.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>7</v>
       </c>
@@ -1891,41 +2731,69 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2">
         <v>82</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="E2" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="25">
+        <f>COUNT(C2:C6)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3">
         <v>79</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="E3" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="26">
+        <f>AVERAGE(C2:C6)</f>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4">
         <v>85</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="E4" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="25">
+        <f>MAX(C2:C6)</f>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>81</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="E5" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="25">
+        <f>MIN(C2:C6)</f>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>83</v>
@@ -1952,7 +2820,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="5" width="11.453125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6328125" style="5" customWidth="1"/>
     <col min="7" max="16384" width="10.90625" style="5"/>
   </cols>
   <sheetData>
@@ -1970,10 +2838,10 @@
         <v>8</v>
       </c>
       <c r="E1" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -1981,70 +2849,70 @@
         <v>46266</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" s="11">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="12">
-        <v>46275</v>
+        <v>46266</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D3" s="11">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="12">
-        <v>46274</v>
+        <v>46267</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D4" s="11">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
-        <v>46274</v>
+        <v>46267</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="11">
         <v>85</v>
@@ -2053,47 +2921,47 @@
         <v>12</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
-        <v>46273</v>
+        <v>46268</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D6" s="11">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D7" s="11">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2101,119 +2969,119 @@
         <v>46269</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D8" s="11">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="12">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D9" s="11">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>12</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D10" s="11">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="12">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="11">
+        <v>86</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="D11" s="11">
-        <v>84</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="12">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D12" s="11">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="12">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D13" s="11">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -2221,119 +3089,119 @@
         <v>46272</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D14" s="11">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>12</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="12">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D15" s="11">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>12</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="12">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D16" s="11">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="12">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="11">
+        <v>87</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="D17" s="11">
-        <v>84</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="12">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D18" s="11">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="12">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D19" s="11">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -2341,45 +3209,46 @@
         <v>46275</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D20" s="11">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="12">
-        <v>46266</v>
+        <v>46275</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D21" s="11">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F21" xr:uid="{5717829A-3788-432D-B9D3-0C993DB4373F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F21">
-    <sortCondition descending="1" ref="A2:A21"/>
-    <sortCondition ref="B2:B21"/>
+    <sortCondition ref="A2:A21"/>
+    <sortCondition ref="D2:D21"/>
   </sortState>
   <customSheetViews>
     <customSheetView guid="{8604812A-736C-47AE-A298-3A6F79AFD00F}">
@@ -2413,196 +3282,196 @@
     <col min="10" max="10" width="19.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:10" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="13" t="s">
+      <c r="I1" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="J1" s="32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="14">
+        <v>120</v>
+      </c>
+      <c r="E2" s="14">
+        <v>135</v>
+      </c>
+      <c r="F2" s="14">
+        <v>15</v>
+      </c>
+      <c r="G2" s="14">
+        <v>82</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="14">
+      <c r="J2" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="13">
         <v>46266</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="14">
+        <v>98</v>
+      </c>
+      <c r="E3" s="14">
+        <v>110</v>
+      </c>
+      <c r="F3" s="14">
+        <v>12</v>
+      </c>
+      <c r="G3" s="14">
+        <v>79</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C4" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="14">
+        <v>150</v>
+      </c>
+      <c r="E4" s="14">
+        <v>162</v>
+      </c>
+      <c r="F4" s="14">
+        <v>12</v>
+      </c>
+      <c r="G4" s="14">
+        <v>85</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="15">
-        <v>120</v>
-      </c>
-      <c r="E2" s="15">
-        <v>135</v>
-      </c>
-      <c r="F2" s="15">
-        <v>15</v>
-      </c>
-      <c r="G2" s="15">
-        <v>82</v>
-      </c>
-      <c r="H2" s="15" t="s">
+      <c r="D5" s="14">
+        <v>130</v>
+      </c>
+      <c r="E5" s="14">
+        <v>142</v>
+      </c>
+      <c r="F5" s="14">
         <v>12</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="15" t="s">
+      <c r="G5" s="14">
+        <v>81</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="14">
+        <v>105</v>
+      </c>
+      <c r="E6" s="14">
+        <v>121</v>
+      </c>
+      <c r="F6" s="14">
+        <v>16</v>
+      </c>
+      <c r="G6" s="14">
+        <v>78</v>
+      </c>
+      <c r="H6" s="14" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="14">
-        <v>46266</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="15">
-        <v>98</v>
-      </c>
-      <c r="E3" s="15">
-        <v>110</v>
-      </c>
-      <c r="F3" s="15">
-        <v>12</v>
-      </c>
-      <c r="G3" s="15">
-        <v>79</v>
-      </c>
-      <c r="H3" s="15" t="s">
+      <c r="I6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="14">
-        <v>46267</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="15">
-        <v>150</v>
-      </c>
-      <c r="E4" s="15">
-        <v>162</v>
-      </c>
-      <c r="F4" s="15">
-        <v>12</v>
-      </c>
-      <c r="G4" s="15">
-        <v>85</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="14">
-        <v>46267</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="15">
-        <v>130</v>
-      </c>
-      <c r="E5" s="15">
-        <v>142</v>
-      </c>
-      <c r="F5" s="15">
-        <v>12</v>
-      </c>
-      <c r="G5" s="15">
-        <v>81</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="15" t="s">
+      <c r="J6" s="14" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="14">
-        <v>46268</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="15">
-        <v>105</v>
-      </c>
-      <c r="E6" s="15">
-        <v>121</v>
-      </c>
-      <c r="F6" s="15">
-        <v>16</v>
-      </c>
-      <c r="G6" s="15">
-        <v>78</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2617,7 +3486,11 @@
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup scale="48" orientation="landscape" r:id="rId2"/>
+  <pageSetup orientation="landscape" r:id="rId2"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"-,Negrita"Documento confidencial&amp;C&amp;D&amp;RPágina &amp;P</oddHeader>
+    <oddFooter>Página &amp;P</oddFooter>
+  </headerFooter>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="10" max="1048575" man="1"/>
   </colBreaks>
@@ -2642,22 +3515,22 @@
         <v>7</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>9</v>
@@ -2689,10 +3562,10 @@
         <v>12</v>
       </c>
       <c r="I2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -2718,13 +3591,13 @@
         <v>79</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
@@ -2735,7 +3608,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="6">
         <v>150</v>
@@ -2753,10 +3626,10 @@
         <v>12</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -2785,10 +3658,10 @@
         <v>12</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -2814,13 +3687,13 @@
         <v>78</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="J6" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
